--- a/file/table/DAPC_Curves.xlsx
+++ b/file/table/DAPC_Curves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C82AB1-D1B8-4370-9A4E-FCF0EC7C3486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA84F21-4394-42B5-8672-643E6C3330BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{9A4D6CE6-1E62-441D-8A43-C5F05171BE31}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Elipse" sheetId="1" r:id="rId1"/>
     <sheet name="Gráfico" sheetId="3" r:id="rId2"/>
     <sheet name="AutoCAD" sheetId="4" r:id="rId3"/>
-    <sheet name="Mettadata" sheetId="5" r:id="rId4"/>
+    <sheet name="Metadata" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="a">Elipse!$D$7</definedName>
@@ -11648,2434 +11648,4036 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E96FD8F5-27BA-4577-AFDE-75F52D7C7DF0}">
-  <dimension ref="A1:A407"/>
+  <dimension ref="A1:B407"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.6640625" style="1"/>
+    <col min="2" max="2" width="33.46484375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C13,",",Elipse!D13)</f>
         <v>100,70</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B2" s="1" t="str">
+        <f>_xlfn.CONCAT("POINT ",A2)</f>
+        <v>POINT 100,70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C14,",",Elipse!$D14)</f>
         <v>101.25,69.9956592511697</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B3" s="1" t="str">
+        <f t="shared" ref="B3:B66" si="0">_xlfn.CONCAT("POINT ",A3)</f>
+        <v>POINT 101.25,69.9956592511697</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C15,",",Elipse!D15)</f>
         <v>102.5,69.9826313471363</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 102.5,69.9826313471363</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C16,",",Elipse!D16)</f>
         <v>103.75,69.9608992783391</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 103.75,69.9608992783391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C17,",",Elipse!D17)</f>
         <v>105,69.9304345718357</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 105,69.9304345718357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C18,",",Elipse!D18)</f>
         <v>106.25,69.8911971038</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 106.25,69.8911971038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C19,",",Elipse!D19)</f>
         <v>107.5,69.8431348329844</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 107.5,69.8431348329844</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C20,",",Elipse!D20)</f>
         <v>108.75,69.7861834509729</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 108.75,69.7861834509729</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C21,",",Elipse!D21)</f>
         <v>110,69.7202659436654</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 110,69.7202659436654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A11" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C22,",",Elipse!D22)</f>
         <v>111.25,69.6452920568771</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 111.25,69.6452920568771</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A12" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C23,",",Elipse!D23)</f>
         <v>112.5,69.5611576571758</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 112.5,69.5611576571758</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A13" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C24,",",Elipse!D24)</f>
         <v>113.75,69.4677439770394</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 113.75,69.4677439770394</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C25,",",Elipse!D25)</f>
         <v>115,69.3649167310371</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 115,69.3649167310371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A15" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C26,",",Elipse!D26)</f>
         <v>116.25,69.2525250869132</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 116.25,69.2525250869132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C27,",",Elipse!D27)</f>
         <v>117.5,69.1304004720817</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 117.5,69.1304004720817</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C28,",",Elipse!D28)</f>
         <v>118.75,68.9983551919633</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 118.75,68.9983551919633</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C29,",",Elipse!D29)</f>
         <v>120,68.8561808316413</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 120,68.8561808316413</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C30,",",Elipse!D30)</f>
         <v>121.25,68.7036464062195</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 121.25,68.7036464062195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A20" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C31,",",Elipse!D31)</f>
         <v>122.5,68.5404962177392</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 122.5,68.5404962177392</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A21" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C32,",",Elipse!D32)</f>
         <v>123.75,68.3664473671118</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 123.75,68.3664473671118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A22" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C33,",",Elipse!D33)</f>
         <v>125,68.1811868577262</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 125,68.1811868577262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A23" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C34,",",Elipse!D34)</f>
         <v>126.25,67.9843682124227</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 126.25,67.9843682124227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A24" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C35,",",Elipse!D35)</f>
         <v>127.5,67.775607506418</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 127.5,67.775607506418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A25" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C36,",",Elipse!D36)</f>
         <v>128.75,67.5544786941174</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 128.75,67.5544786941174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A26" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C37,",",Elipse!D37)</f>
         <v>130,67.3205080756888</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 130,67.3205080756888</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A27" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C38,",",Elipse!D38)</f>
         <v>131.25,67.0731677071232</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 131.25,67.0731677071232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A28" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C39,",",Elipse!D39)</f>
         <v>132.5,66.8118675015267</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 132.5,66.8118675015267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A29" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C40,",",Elipse!D40)</f>
         <v>133.75,66.5359456941537</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 133.75,66.5359456941537</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A30" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C41,",",Elipse!D41)</f>
         <v>135,66.2446572413483</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 135,66.2446572413483</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A31" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C42,",",Elipse!D42)</f>
         <v>136.25,65.9371595824211</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 136.25,65.9371595824211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A32" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C43,",",Elipse!D43)</f>
         <v>137.5,65.612494995996</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 137.5,65.612494995996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A33" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C44,",",Elipse!D44)</f>
         <v>138.75,65.2695685015073</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 138.75,65.2695685015073</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A34" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C45,",",Elipse!D45)</f>
         <v>140,64.9071198499986</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 140,64.9071198499986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A35" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C46,",",Elipse!D46)</f>
         <v>141.25,64.5236875482778</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 141.25,64.5236875482778</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A36" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C47,",",Elipse!D47)</f>
         <v>142.5,64.1175619550812</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 142.5,64.1175619550812</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A37" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C48,",",Elipse!D48)</f>
         <v>143.75,63.6867230880474</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 143.75,63.6867230880474</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A38" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C49,",",Elipse!D49)</f>
         <v>145,63.228756555323</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 145,63.228756555323</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A39" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C50,",",Elipse!D50)</f>
         <v>146.25,62.7407373761839</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 146.25,62.7407373761839</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A40" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C51,",",Elipse!D51)</f>
         <v>147.5,62.219065248846</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 147.5,62.219065248846</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A41" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C52,",",Elipse!D52)</f>
         <v>148.75,61.659223816361</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 148.75,61.659223816361</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A42" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C53,",",Elipse!D53)</f>
         <v>150,61.0554159678513</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 150,61.0554159678513</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A43" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C54,",",Elipse!D54)</f>
         <v>151.25,60.3999866452906</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 151.25,60.3999866452906</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A44" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C55,",",Elipse!D55)</f>
         <v>152.5,59.6824583655185</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 152.5,59.6824583655185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A45" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C56,",",Elipse!D56)</f>
         <v>153.75,58.887803753209</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 153.75,58.887803753209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A46" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C57,",",Elipse!D57)</f>
         <v>155,57.9930525388545</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 155,57.9930525388545</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A47" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C58,",",Elipse!D58)</f>
         <v>156.25,56.9597054535375</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 156.25,56.9597054535375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A48" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C59,",",Elipse!D59)</f>
         <v>157.5,55.7130455003342</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 157.5,55.7130455003342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A49" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C60,",",Elipse!D60)</f>
         <v>158.75,54.0611643103371</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 158.75,54.0611643103371</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A50" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C61,",",Elipse!D61)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A51" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C62,",",Elipse!D62)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A52" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C63,",",Elipse!D63)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A53" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C64,",",Elipse!D64)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A54" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C65,",",Elipse!D65)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A55" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C66,",",Elipse!D66)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A56" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C67,",",Elipse!D67)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A57" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C68,",",Elipse!D68)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A58" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C69,",",Elipse!D69)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A59" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C70,",",Elipse!D70)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A60" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C71,",",Elipse!D71)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A61" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C72,",",Elipse!D72)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A62" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C73,",",Elipse!D73)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A63" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C74,",",Elipse!D74)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A64" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C75,",",Elipse!D75)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A65" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C76,",",Elipse!D76)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A66" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C77,",",Elipse!D77)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B66" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A67" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C78,",",Elipse!D78)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B67" s="1" t="str">
+        <f t="shared" ref="B67:B101" si="1">_xlfn.CONCAT("POINT ",A67)</f>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A68" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C79,",",Elipse!D79)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A69" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C80,",",Elipse!D80)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A70" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C81,",",Elipse!D81)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A71" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C82,",",Elipse!D82)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B71" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A72" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C83,",",Elipse!D83)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B72" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A73" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C84,",",Elipse!D84)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B73" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A74" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C85,",",Elipse!D85)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B74" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A75" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C86,",",Elipse!D86)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B75" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A76" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C87,",",Elipse!D87)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B76" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A77" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C88,",",Elipse!D88)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B77" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A78" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C89,",",Elipse!D89)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B78" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A79" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C90,",",Elipse!D90)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B79" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A80" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C91,",",Elipse!D91)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B80" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A81" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C92,",",Elipse!D92)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B81" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A82" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C93,",",Elipse!D93)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B82" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A83" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C94,",",Elipse!D94)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B83" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A84" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C95,",",Elipse!D95)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B84" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A85" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C96,",",Elipse!D96)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B85" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A86" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C97,",",Elipse!D97)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B86" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A87" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C98,",",Elipse!D98)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B87" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A88" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C99,",",Elipse!D99)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B88" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A89" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C100,",",Elipse!D100)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B89" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A90" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C101,",",Elipse!D101)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B90" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A91" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C102,",",Elipse!D102)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B91" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A92" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C103,",",Elipse!D103)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B92" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A93" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C104,",",Elipse!D104)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B93" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A94" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C105,",",Elipse!D105)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B94" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A95" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C106,",",Elipse!D106)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B95" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A96" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C107,",",Elipse!D107)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B96" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A97" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C108,",",Elipse!D108)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A98" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C109,",",Elipse!D109)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B98" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A99" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C110,",",Elipse!D110)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B99" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A100" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C111,",",Elipse!D111)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A101" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!C112,",",Elipse!D112)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B101" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A103" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A104" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C13,",",Elipse!E13)</f>
         <v>100,30</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B104" s="1" t="str">
+        <f t="shared" ref="B104:B167" si="2">_xlfn.CONCAT("POINT ",A104)</f>
+        <v>POINT 100,30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A105" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C14,",",Elipse!E14)</f>
         <v>101.25,30.0043407488303</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B105" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 101.25,30.0043407488303</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A106" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C15,",",Elipse!E15)</f>
         <v>102.5,30.0173686528637</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B106" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 102.5,30.0173686528637</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A107" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C16,",",Elipse!E16)</f>
         <v>103.75,30.0391007216609</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B107" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 103.75,30.0391007216609</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A108" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C17,",",Elipse!E17)</f>
         <v>105,30.0695654281643</v>
       </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B108" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 105,30.0695654281643</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A109" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C18,",",Elipse!E18)</f>
         <v>106.25,30.1088028962</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B109" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 106.25,30.1088028962</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A110" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C19,",",Elipse!E19)</f>
         <v>107.5,30.1568651670156</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B110" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 107.5,30.1568651670156</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A111" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C20,",",Elipse!E20)</f>
         <v>108.75,30.2138165490271</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B111" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 108.75,30.2138165490271</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A112" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C21,",",Elipse!E21)</f>
         <v>110,30.2797340563346</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B112" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 110,30.2797340563346</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A113" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C22,",",Elipse!E22)</f>
         <v>111.25,30.3547079431229</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B113" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 111.25,30.3547079431229</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A114" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C23,",",Elipse!E23)</f>
         <v>112.5,30.4388423428242</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B114" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 112.5,30.4388423428242</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A115" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C24,",",Elipse!E24)</f>
         <v>113.75,30.5322560229606</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B115" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 113.75,30.5322560229606</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A116" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C25,",",Elipse!E25)</f>
         <v>115,30.6350832689629</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B116" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 115,30.6350832689629</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A117" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C26,",",Elipse!E26)</f>
         <v>116.25,30.7474749130868</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B117" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 116.25,30.7474749130868</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A118" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C27,",",Elipse!E27)</f>
         <v>117.5,30.8695995279183</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B118" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 117.5,30.8695995279183</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A119" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C28,",",Elipse!E28)</f>
         <v>118.75,31.0016448080367</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B119" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 118.75,31.0016448080367</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A120" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C29,",",Elipse!E29)</f>
         <v>120,31.1438191683587</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B120" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 120,31.1438191683587</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A121" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C30,",",Elipse!E30)</f>
         <v>121.25,31.2963535937805</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B121" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 121.25,31.2963535937805</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A122" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C31,",",Elipse!E31)</f>
         <v>122.5,31.4595037822608</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B122" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 122.5,31.4595037822608</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A123" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C32,",",Elipse!E32)</f>
         <v>123.75,31.6335526328882</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B123" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 123.75,31.6335526328882</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A124" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C33,",",Elipse!E33)</f>
         <v>125,31.8188131422738</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B124" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 125,31.8188131422738</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A125" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C34,",",Elipse!E34)</f>
         <v>126.25,32.0156317875773</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B125" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 126.25,32.0156317875773</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A126" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C35,",",Elipse!E35)</f>
         <v>127.5,32.224392493582</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B126" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 127.5,32.224392493582</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A127" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C36,",",Elipse!E36)</f>
         <v>128.75,32.4455213058826</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B127" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 128.75,32.4455213058826</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A128" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C37,",",Elipse!E37)</f>
         <v>130,32.6794919243112</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B128" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 130,32.6794919243112</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A129" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C38,",",Elipse!E38)</f>
         <v>131.25,32.9268322928768</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B129" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 131.25,32.9268322928768</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A130" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C39,",",Elipse!E39)</f>
         <v>132.5,33.1881324984733</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B130" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 132.5,33.1881324984733</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A131" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C40,",",Elipse!E40)</f>
         <v>133.75,33.4640543058463</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B131" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 133.75,33.4640543058463</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A132" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C41,",",Elipse!E41)</f>
         <v>135,33.7553427586517</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B132" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 135,33.7553427586517</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A133" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C42,",",Elipse!E42)</f>
         <v>136.25,34.0628404175789</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B133" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 136.25,34.0628404175789</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A134" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C43,",",Elipse!E43)</f>
         <v>137.5,34.387505004004</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B134" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 137.5,34.387505004004</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A135" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C44,",",Elipse!E44)</f>
         <v>138.75,34.7304314984927</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B135" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 138.75,34.7304314984927</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A136" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C45,",",Elipse!E45)</f>
         <v>140,35.0928801500014</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B136" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 140,35.0928801500014</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A137" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C46,",",Elipse!E46)</f>
         <v>141.25,35.4763124517222</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B137" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 141.25,35.4763124517222</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A138" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C47,",",Elipse!E47)</f>
         <v>142.5,35.8824380449188</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B138" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 142.5,35.8824380449188</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A139" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C48,",",Elipse!E48)</f>
         <v>143.75,36.3132769119526</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B139" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 143.75,36.3132769119526</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A140" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C49,",",Elipse!E49)</f>
         <v>145,36.771243444677</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B140" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 145,36.771243444677</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A141" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C50,",",Elipse!E50)</f>
         <v>146.25,37.2592626238161</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B141" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 146.25,37.2592626238161</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A142" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C51,",",Elipse!E51)</f>
         <v>147.5,37.780934751154</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B142" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 147.5,37.780934751154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A143" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C52,",",Elipse!E52)</f>
         <v>148.75,38.340776183639</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B143" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 148.75,38.340776183639</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A144" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C53,",",Elipse!E53)</f>
         <v>150,38.9445840321487</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B144" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 150,38.9445840321487</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A145" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C54,",",Elipse!E54)</f>
         <v>151.25,39.6000133547094</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B145" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 151.25,39.6000133547094</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A146" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C55,",",Elipse!E55)</f>
         <v>152.5,40.3175416344815</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B146" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 152.5,40.3175416344815</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A147" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C56,",",Elipse!E56)</f>
         <v>153.75,41.112196246791</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B147" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 153.75,41.112196246791</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A148" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C57,",",Elipse!E57)</f>
         <v>155,42.0069474611455</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B148" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 155,42.0069474611455</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A149" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C58,",",Elipse!E58)</f>
         <v>156.25,43.0402945464625</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B149" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 156.25,43.0402945464625</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A150" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C59,",",Elipse!E59)</f>
         <v>157.5,44.2869544996658</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B150" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 157.5,44.2869544996658</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A151" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C60,",",Elipse!E60)</f>
         <v>158.75,45.9388356896629</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B151" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 158.75,45.9388356896629</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A152" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C61,",",Elipse!E61)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B152" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A153" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C62,",",Elipse!E62)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B153" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A154" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C63,",",Elipse!E63)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B154" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A155" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C64,",",Elipse!E64)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B155" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A156" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C65,",",Elipse!E65)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B156" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A157" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C66,",",Elipse!E66)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B157" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A158" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C67,",",Elipse!E67)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B158" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A159" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C68,",",Elipse!E68)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B159" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A160" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C69,",",Elipse!E69)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B160" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A161" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C70,",",Elipse!E70)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B161" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A162" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C71,",",Elipse!E71)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B162" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A163" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C72,",",Elipse!E72)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B163" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A164" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C73,",",Elipse!E73)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B164" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A165" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C74,",",Elipse!E74)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B165" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A166" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C75,",",Elipse!E75)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B166" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A167" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C76,",",Elipse!E76)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B167" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A168" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C77,",",Elipse!E77)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B168" s="1" t="str">
+        <f t="shared" ref="B168:B203" si="3">_xlfn.CONCAT("POINT ",A168)</f>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A169" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C78,",",Elipse!E78)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B169" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A170" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C79,",",Elipse!E79)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B170" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A171" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C80,",",Elipse!E80)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B171" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A172" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C81,",",Elipse!E81)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B172" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A173" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C82,",",Elipse!E82)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B173" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A174" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C83,",",Elipse!E83)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B174" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A175" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C84,",",Elipse!E84)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B175" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A176" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C85,",",Elipse!E85)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B176" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A177" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C86,",",Elipse!E86)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B177" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A178" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C87,",",Elipse!E87)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B178" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A179" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C88,",",Elipse!E88)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B179" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A180" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C89,",",Elipse!E89)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B180" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A181" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C90,",",Elipse!E90)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B181" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A182" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C91,",",Elipse!E91)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B182" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A183" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C92,",",Elipse!E92)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B183" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A184" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C93,",",Elipse!E93)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B184" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A185" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C94,",",Elipse!E94)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B185" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A186" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C95,",",Elipse!E95)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B186" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A187" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C96,",",Elipse!E96)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B187" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A188" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C97,",",Elipse!E97)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B188" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A189" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C98,",",Elipse!E98)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B189" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A190" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C99,",",Elipse!E99)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B190" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A191" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C100,",",Elipse!E100)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B191" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A192" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C101,",",Elipse!E101)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B192" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A193" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C102,",",Elipse!E102)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B193" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A194" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C103,",",Elipse!E103)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B194" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A195" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C104,",",Elipse!E104)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B195" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A196" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C105,",",Elipse!E105)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B196" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A197" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C106,",",Elipse!E106)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B197" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A198" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C107,",",Elipse!E107)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B198" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A199" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C108,",",Elipse!E108)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B199" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A200" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C109,",",Elipse!E109)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B200" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A201" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C110,",",Elipse!E110)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B201" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A202" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C111,",",Elipse!E111)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B202" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A203" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$C112,",",Elipse!E112)</f>
         <v>160,50</v>
       </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B203" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>POINT 160,50</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A205" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A206" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F13,",",Elipse!G13)</f>
         <v>100,70</v>
       </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B206" s="1" t="str">
+        <f t="shared" ref="B206:B269" si="4">_xlfn.CONCAT("POINT ",A206)</f>
+        <v>POINT 100,70</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A207" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F14,",",Elipse!G14)</f>
         <v>98.75,69.9956592511697</v>
       </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B207" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 98.75,69.9956592511697</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A208" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F15,",",Elipse!G15)</f>
         <v>97.5,69.9826313471363</v>
       </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B208" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 97.5,69.9826313471363</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A209" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F16,",",Elipse!G16)</f>
         <v>96.25,69.9608992783391</v>
       </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B209" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 96.25,69.9608992783391</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A210" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F17,",",Elipse!G17)</f>
         <v>95,69.9304345718357</v>
       </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B210" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 95,69.9304345718357</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A211" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F18,",",Elipse!G18)</f>
         <v>93.75,69.8911971038</v>
       </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B211" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 93.75,69.8911971038</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A212" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F19,",",Elipse!G19)</f>
         <v>92.5,69.8431348329844</v>
       </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B212" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 92.5,69.8431348329844</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A213" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F20,",",Elipse!G20)</f>
         <v>91.25,69.7861834509729</v>
       </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B213" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 91.25,69.7861834509729</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A214" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F21,",",Elipse!G21)</f>
         <v>90,69.7202659436654</v>
       </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B214" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 90,69.7202659436654</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A215" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F22,",",Elipse!G22)</f>
         <v>88.75,69.6452920568771</v>
       </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B215" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 88.75,69.6452920568771</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A216" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F23,",",Elipse!G23)</f>
         <v>87.5,69.5611576571758</v>
       </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B216" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 87.5,69.5611576571758</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A217" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F24,",",Elipse!G24)</f>
         <v>86.25,69.4677439770394</v>
       </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B217" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 86.25,69.4677439770394</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A218" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F25,",",Elipse!G25)</f>
         <v>85,69.3649167310371</v>
       </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B218" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 85,69.3649167310371</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A219" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F26,",",Elipse!G26)</f>
         <v>83.75,69.2525250869132</v>
       </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B219" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 83.75,69.2525250869132</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A220" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F27,",",Elipse!G27)</f>
         <v>82.5,69.1304004720817</v>
       </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B220" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 82.5,69.1304004720817</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A221" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F28,",",Elipse!G28)</f>
         <v>81.25,68.9983551919633</v>
       </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B221" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 81.25,68.9983551919633</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A222" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F29,",",Elipse!G29)</f>
         <v>80,68.8561808316413</v>
       </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B222" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 80,68.8561808316413</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A223" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F30,",",Elipse!G30)</f>
         <v>78.75,68.7036464062195</v>
       </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B223" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 78.75,68.7036464062195</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A224" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F31,",",Elipse!G31)</f>
         <v>77.5,68.5404962177392</v>
       </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B224" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 77.5,68.5404962177392</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A225" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F32,",",Elipse!G32)</f>
         <v>76.25,68.3664473671118</v>
       </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B225" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 76.25,68.3664473671118</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A226" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F33,",",Elipse!G33)</f>
         <v>75,68.1811868577262</v>
       </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B226" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 75,68.1811868577262</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A227" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F34,",",Elipse!G34)</f>
         <v>73.75,67.9843682124227</v>
       </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B227" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 73.75,67.9843682124227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A228" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F35,",",Elipse!G35)</f>
         <v>72.5,67.775607506418</v>
       </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B228" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 72.5,67.775607506418</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A229" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F36,",",Elipse!G36)</f>
         <v>71.25,67.5544786941174</v>
       </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B229" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 71.25,67.5544786941174</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A230" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F37,",",Elipse!G37)</f>
         <v>70,67.3205080756888</v>
       </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B230" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 70,67.3205080756888</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A231" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F38,",",Elipse!G38)</f>
         <v>68.75,67.0731677071232</v>
       </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B231" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 68.75,67.0731677071232</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A232" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F39,",",Elipse!G39)</f>
         <v>67.5,66.8118675015267</v>
       </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B232" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 67.5,66.8118675015267</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A233" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F40,",",Elipse!G40)</f>
         <v>66.25,66.5359456941537</v>
       </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B233" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 66.25,66.5359456941537</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A234" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F41,",",Elipse!G41)</f>
         <v>65,66.2446572413483</v>
       </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B234" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 65,66.2446572413483</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A235" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F42,",",Elipse!G42)</f>
         <v>63.75,65.9371595824211</v>
       </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B235" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 63.75,65.9371595824211</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A236" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F43,",",Elipse!G43)</f>
         <v>62.5,65.612494995996</v>
       </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B236" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 62.5,65.612494995996</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A237" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F44,",",Elipse!G44)</f>
         <v>61.25,65.2695685015073</v>
       </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B237" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 61.25,65.2695685015073</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A238" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F45,",",Elipse!G45)</f>
         <v>60,64.9071198499986</v>
       </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B238" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 60,64.9071198499986</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A239" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F46,",",Elipse!G46)</f>
         <v>58.75,64.5236875482778</v>
       </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B239" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 58.75,64.5236875482778</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A240" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F47,",",Elipse!G47)</f>
         <v>57.5,64.1175619550812</v>
       </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B240" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 57.5,64.1175619550812</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A241" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F48,",",Elipse!G48)</f>
         <v>56.25,63.6867230880474</v>
       </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B241" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 56.25,63.6867230880474</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A242" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F49,",",Elipse!G49)</f>
         <v>55,63.228756555323</v>
       </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B242" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 55,63.228756555323</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A243" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F50,",",Elipse!G50)</f>
         <v>53.75,62.7407373761839</v>
       </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B243" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 53.75,62.7407373761839</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A244" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F51,",",Elipse!G51)</f>
         <v>52.5,62.219065248846</v>
       </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B244" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 52.5,62.219065248846</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A245" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F52,",",Elipse!G52)</f>
         <v>51.25,61.659223816361</v>
       </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B245" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 51.25,61.659223816361</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A246" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F53,",",Elipse!G53)</f>
         <v>50,61.0554159678513</v>
       </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B246" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 50,61.0554159678513</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A247" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F54,",",Elipse!G54)</f>
         <v>48.75,60.3999866452906</v>
       </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B247" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 48.75,60.3999866452906</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A248" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F55,",",Elipse!G55)</f>
         <v>47.5,59.6824583655185</v>
       </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B248" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 47.5,59.6824583655185</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A249" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F56,",",Elipse!G56)</f>
         <v>46.25,58.887803753209</v>
       </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B249" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 46.25,58.887803753209</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A250" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F57,",",Elipse!G57)</f>
         <v>45,57.9930525388545</v>
       </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B250" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 45,57.9930525388545</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A251" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F58,",",Elipse!G58)</f>
         <v>43.75,56.9597054535375</v>
       </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B251" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 43.75,56.9597054535375</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A252" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F59,",",Elipse!G59)</f>
         <v>42.5,55.7130455003342</v>
       </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B252" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 42.5,55.7130455003342</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A253" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F60,",",Elipse!G60)</f>
         <v>41.25,54.0611643103371</v>
       </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B253" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 41.25,54.0611643103371</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A254" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F61,",",Elipse!G61)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B254" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A255" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F62,",",Elipse!G62)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B255" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A256" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F63,",",Elipse!G63)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B256" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A257" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F64,",",Elipse!G64)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B257" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A258" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F65,",",Elipse!G65)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B258" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A259" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F66,",",Elipse!G66)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B259" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A260" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F67,",",Elipse!G67)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B260" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A261" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F68,",",Elipse!G68)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B261" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A262" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F69,",",Elipse!G69)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B262" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A263" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F70,",",Elipse!G70)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B263" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A264" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F71,",",Elipse!G71)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B264" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A265" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F72,",",Elipse!G72)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B265" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A266" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F73,",",Elipse!G73)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B266" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A267" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F74,",",Elipse!G74)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B267" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A268" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F75,",",Elipse!G75)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B268" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A269" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F76,",",Elipse!G76)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B269" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A270" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F77,",",Elipse!G77)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B270" s="1" t="str">
+        <f t="shared" ref="B270:B305" si="5">_xlfn.CONCAT("POINT ",A270)</f>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A271" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F78,",",Elipse!G78)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B271" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A272" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F79,",",Elipse!G79)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B272" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A273" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F80,",",Elipse!G80)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B273" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A274" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F81,",",Elipse!G81)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B274" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A275" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F82,",",Elipse!G82)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B275" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A276" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F83,",",Elipse!G83)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B276" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A277" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F84,",",Elipse!G84)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B277" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A278" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F85,",",Elipse!G85)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B278" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A279" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F86,",",Elipse!G86)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B279" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A280" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F87,",",Elipse!G87)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B280" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A281" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F88,",",Elipse!G88)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B281" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A282" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F89,",",Elipse!G89)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B282" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A283" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F90,",",Elipse!G90)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B283" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A284" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F91,",",Elipse!G91)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B284" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A285" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F92,",",Elipse!G92)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B285" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A286" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F93,",",Elipse!G93)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B286" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A287" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F94,",",Elipse!G94)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B287" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A288" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F95,",",Elipse!G95)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B288" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A289" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F96,",",Elipse!G96)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B289" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A290" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F97,",",Elipse!G97)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B290" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A291" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F98,",",Elipse!G98)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B291" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A292" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F99,",",Elipse!G99)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B292" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A293" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F100,",",Elipse!G100)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B293" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A294" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F101,",",Elipse!G101)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B294" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A295" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F102,",",Elipse!G102)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B295" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A296" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F103,",",Elipse!G103)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B296" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A297" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F104,",",Elipse!G104)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B297" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A298" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F105,",",Elipse!G105)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B298" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A299" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F106,",",Elipse!G106)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B299" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A300" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F107,",",Elipse!G107)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B300" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A301" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F108,",",Elipse!G108)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B301" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A302" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F109,",",Elipse!G109)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B302" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A303" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F110,",",Elipse!G110)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B303" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A304" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F111,",",Elipse!G111)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B304" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A305" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F112,",",Elipse!G112)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B305" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A307" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A308" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F13,",",Elipse!H13)</f>
         <v>100,30</v>
       </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B308" s="1" t="str">
+        <f t="shared" ref="B308:B371" si="6">_xlfn.CONCAT("POINT ",A308)</f>
+        <v>POINT 100,30</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A309" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F14,",",Elipse!H14)</f>
         <v>98.75,30.0043407488303</v>
       </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B309" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 98.75,30.0043407488303</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A310" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F15,",",Elipse!H15)</f>
         <v>97.5,30.0173686528637</v>
       </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B310" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 97.5,30.0173686528637</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A311" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F16,",",Elipse!H16)</f>
         <v>96.25,30.0391007216609</v>
       </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B311" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 96.25,30.0391007216609</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A312" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F17,",",Elipse!H17)</f>
         <v>95,30.0695654281643</v>
       </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B312" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 95,30.0695654281643</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A313" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F18,",",Elipse!H18)</f>
         <v>93.75,30.1088028962</v>
       </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B313" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 93.75,30.1088028962</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A314" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F19,",",Elipse!H19)</f>
         <v>92.5,30.1568651670156</v>
       </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B314" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 92.5,30.1568651670156</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A315" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F20,",",Elipse!H20)</f>
         <v>91.25,30.2138165490271</v>
       </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B315" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 91.25,30.2138165490271</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A316" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F21,",",Elipse!H21)</f>
         <v>90,30.2797340563346</v>
       </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B316" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 90,30.2797340563346</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A317" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F22,",",Elipse!H22)</f>
         <v>88.75,30.3547079431229</v>
       </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B317" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 88.75,30.3547079431229</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A318" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F23,",",Elipse!H23)</f>
         <v>87.5,30.4388423428242</v>
       </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B318" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 87.5,30.4388423428242</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A319" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F24,",",Elipse!H24)</f>
         <v>86.25,30.5322560229606</v>
       </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B319" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 86.25,30.5322560229606</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A320" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F25,",",Elipse!H25)</f>
         <v>85,30.6350832689629</v>
       </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B320" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 85,30.6350832689629</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A321" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F26,",",Elipse!H26)</f>
         <v>83.75,30.7474749130868</v>
       </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B321" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 83.75,30.7474749130868</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A322" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F27,",",Elipse!H27)</f>
         <v>82.5,30.8695995279183</v>
       </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B322" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 82.5,30.8695995279183</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A323" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F28,",",Elipse!H28)</f>
         <v>81.25,31.0016448080367</v>
       </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B323" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 81.25,31.0016448080367</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A324" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F29,",",Elipse!H29)</f>
         <v>80,31.1438191683587</v>
       </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B324" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 80,31.1438191683587</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A325" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F30,",",Elipse!H30)</f>
         <v>78.75,31.2963535937805</v>
       </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B325" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 78.75,31.2963535937805</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A326" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F31,",",Elipse!H31)</f>
         <v>77.5,31.4595037822608</v>
       </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B326" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 77.5,31.4595037822608</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A327" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F32,",",Elipse!H32)</f>
         <v>76.25,31.6335526328882</v>
       </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B327" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 76.25,31.6335526328882</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A328" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F33,",",Elipse!H33)</f>
         <v>75,31.8188131422738</v>
       </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B328" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 75,31.8188131422738</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A329" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F34,",",Elipse!H34)</f>
         <v>73.75,32.0156317875773</v>
       </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B329" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 73.75,32.0156317875773</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A330" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F35,",",Elipse!H35)</f>
         <v>72.5,32.224392493582</v>
       </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B330" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 72.5,32.224392493582</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A331" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F36,",",Elipse!H36)</f>
         <v>71.25,32.4455213058826</v>
       </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B331" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 71.25,32.4455213058826</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A332" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F37,",",Elipse!H37)</f>
         <v>70,32.6794919243112</v>
       </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B332" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 70,32.6794919243112</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A333" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F38,",",Elipse!H38)</f>
         <v>68.75,32.9268322928768</v>
       </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B333" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 68.75,32.9268322928768</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A334" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F39,",",Elipse!H39)</f>
         <v>67.5,33.1881324984733</v>
       </c>
-    </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B334" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 67.5,33.1881324984733</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A335" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F40,",",Elipse!H40)</f>
         <v>66.25,33.4640543058463</v>
       </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B335" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 66.25,33.4640543058463</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A336" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F41,",",Elipse!H41)</f>
         <v>65,33.7553427586517</v>
       </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B336" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 65,33.7553427586517</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A337" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F42,",",Elipse!H42)</f>
         <v>63.75,34.0628404175789</v>
       </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B337" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 63.75,34.0628404175789</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A338" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F43,",",Elipse!H43)</f>
         <v>62.5,34.387505004004</v>
       </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B338" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 62.5,34.387505004004</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A339" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F44,",",Elipse!H44)</f>
         <v>61.25,34.7304314984927</v>
       </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B339" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 61.25,34.7304314984927</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A340" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F45,",",Elipse!H45)</f>
         <v>60,35.0928801500014</v>
       </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B340" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 60,35.0928801500014</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A341" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F46,",",Elipse!H46)</f>
         <v>58.75,35.4763124517222</v>
       </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B341" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 58.75,35.4763124517222</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A342" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F47,",",Elipse!H47)</f>
         <v>57.5,35.8824380449188</v>
       </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B342" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 57.5,35.8824380449188</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A343" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F48,",",Elipse!H48)</f>
         <v>56.25,36.3132769119526</v>
       </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B343" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 56.25,36.3132769119526</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A344" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F49,",",Elipse!H49)</f>
         <v>55,36.771243444677</v>
       </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B344" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 55,36.771243444677</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A345" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F50,",",Elipse!H50)</f>
         <v>53.75,37.2592626238161</v>
       </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B345" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 53.75,37.2592626238161</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A346" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F51,",",Elipse!H51)</f>
         <v>52.5,37.780934751154</v>
       </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B346" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 52.5,37.780934751154</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A347" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F52,",",Elipse!H52)</f>
         <v>51.25,38.340776183639</v>
       </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B347" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 51.25,38.340776183639</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A348" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F53,",",Elipse!H53)</f>
         <v>50,38.9445840321487</v>
       </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B348" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 50,38.9445840321487</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A349" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F54,",",Elipse!H54)</f>
         <v>48.75,39.6000133547094</v>
       </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B349" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 48.75,39.6000133547094</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A350" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F55,",",Elipse!H55)</f>
         <v>47.5,40.3175416344815</v>
       </c>
-    </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B350" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 47.5,40.3175416344815</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A351" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F56,",",Elipse!H56)</f>
         <v>46.25,41.112196246791</v>
       </c>
-    </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B351" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 46.25,41.112196246791</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A352" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F57,",",Elipse!H57)</f>
         <v>45,42.0069474611455</v>
       </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B352" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 45,42.0069474611455</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A353" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F58,",",Elipse!H58)</f>
         <v>43.75,43.0402945464625</v>
       </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B353" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 43.75,43.0402945464625</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A354" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F59,",",Elipse!H59)</f>
         <v>42.5,44.2869544996658</v>
       </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B354" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 42.5,44.2869544996658</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A355" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F60,",",Elipse!H60)</f>
         <v>41.25,45.9388356896629</v>
       </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B355" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 41.25,45.9388356896629</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A356" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F61,",",Elipse!H61)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B356" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A357" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F62,",",Elipse!H62)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B357" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A358" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F63,",",Elipse!H63)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B358" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A359" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F64,",",Elipse!H64)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B359" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A360" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F65,",",Elipse!H65)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B360" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A361" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F66,",",Elipse!H66)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B361" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A362" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F67,",",Elipse!H67)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B362" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A363" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F68,",",Elipse!H68)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B363" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A364" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F69,",",Elipse!H69)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B364" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A365" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F70,",",Elipse!H70)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B365" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A366" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F71,",",Elipse!H71)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B366" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A367" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F72,",",Elipse!H72)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B367" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A368" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F73,",",Elipse!H73)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B368" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A369" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F74,",",Elipse!H74)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B369" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A370" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F75,",",Elipse!H75)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B370" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A371" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F76,",",Elipse!H76)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B371" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A372" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F77,",",Elipse!H77)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B372" s="1" t="str">
+        <f t="shared" ref="B372:B407" si="7">_xlfn.CONCAT("POINT ",A372)</f>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A373" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F78,",",Elipse!H78)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B373" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A374" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F79,",",Elipse!H79)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B374" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A375" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F80,",",Elipse!H80)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B375" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A376" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F81,",",Elipse!H81)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B376" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A377" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F82,",",Elipse!H82)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B377" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A378" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F83,",",Elipse!H83)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B378" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A379" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F84,",",Elipse!H84)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B379" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A380" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F85,",",Elipse!H85)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B380" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A381" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F86,",",Elipse!H86)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B381" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A382" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F87,",",Elipse!H87)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B382" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A383" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F88,",",Elipse!H88)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B383" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A384" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F89,",",Elipse!H89)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B384" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A385" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F90,",",Elipse!H90)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B385" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A386" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F91,",",Elipse!H91)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B386" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A387" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F92,",",Elipse!H92)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B387" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A388" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F93,",",Elipse!H93)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B388" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A389" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F94,",",Elipse!H94)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B389" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A390" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F95,",",Elipse!H95)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B390" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A391" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F96,",",Elipse!H96)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B391" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A392" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F97,",",Elipse!H97)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B392" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A393" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F98,",",Elipse!H98)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B393" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A394" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F99,",",Elipse!H99)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B394" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A395" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F100,",",Elipse!H100)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B395" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A396" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F101,",",Elipse!H101)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B396" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A397" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F102,",",Elipse!H102)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B397" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A398" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F103,",",Elipse!H103)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B398" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A399" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F104,",",Elipse!H104)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B399" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A400" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F105,",",Elipse!H105)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B400" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A401" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F106,",",Elipse!H106)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B401" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A402" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F107,",",Elipse!H107)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B402" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A403" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F108,",",Elipse!H108)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B403" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A404" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F109,",",Elipse!H109)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B404" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A405" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F110,",",Elipse!H110)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B405" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A406" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F111,",",Elipse!H111)</f>
         <v>40,50</v>
       </c>
-    </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.6">
+      <c r="B406" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A407" s="1" t="str">
         <f>_xlfn.CONCAT(Elipse!$F112,",",Elipse!H112)</f>
         <v>40,50</v>
       </c>
+      <c r="B407" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>POINT 40,50</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ic62sOGS686REBd6a+O1du90x33/djAX/sPXBQxlQLqQW5aFATuQ2t/oXwKbyhMxzdY5RTSXBX7c2ul81/aP2g==" saltValue="L8NdhpzGfjAnTFTKRLi1pw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14106,6 +15708,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="LTdCJyVS2iykCmUD2QgLoTMChQxGkNUmEr03z/0aP8bv2Ct3a4W1bRsTzKra/KtVTE6bpCq8zVJQmhvaBdsIGw==" saltValue="58u1yoSQOyWDVTXjY+2/+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/file/table/DAPC_Curves.xlsx
+++ b/file/table/DAPC_Curves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29114"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB94F358-CFDD-4C30-8C52-F8909D483F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEB8961-ED12-410E-AB40-CDCA160B2391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="684" xr2:uid="{9A4D6CE6-1E62-441D-8A43-C5F05171BE31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="684" firstSheet="1" activeTab="5" xr2:uid="{9A4D6CE6-1E62-441D-8A43-C5F05171BE31}"/>
   </bookViews>
   <sheets>
     <sheet name="ElipseTabla" sheetId="1" r:id="rId1"/>
@@ -812,7 +812,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1463,7 +1463,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -2114,7 +2114,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -2765,7 +2765,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
@@ -3441,10 +3441,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3473,10 +3470,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3495,10 +3489,7 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3511,10 +3502,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3557,10 +3545,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3589,10 +3574,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3611,10 +3593,7 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3627,10 +3606,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3679,6 +3655,9 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
           <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
           <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
         </a:defRPr>
@@ -3695,6 +3674,2912 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.2422226387707333"/>
+          <c:y val="5.7846457456438752E-2"/>
+          <c:w val="0.67161910804146896"/>
+          <c:h val="0.67803249743379446"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ElipseTabla!$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YC1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$C$14:$C$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>101.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>103.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>106.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>107.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>108.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>111.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>113.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>116.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>117.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>118.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>121.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>122.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>123.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>127.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>128.75</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>131.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>132.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>133.75</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>136.25</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>137.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>138.75</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>141.25</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>142.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>143.75</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>146.25</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>147.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>148.75</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>151.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>152.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>153.75</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>156.25</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>157.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>158.75</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$D$14:$D$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69.995659251169712</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69.982631347136333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.960899278339141</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69.930434571835661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.89119710380001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.843134832984433</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.786183450972942</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>69.720265943665382</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69.645292056877139</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.561157657175841</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>69.467743977039447</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>69.364916731037084</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>69.252525086913209</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>69.130400472081661</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>68.998355191963327</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>68.856180831641268</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>68.703646406219534</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>68.540496217739161</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>68.366447367111817</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>68.181186857726189</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>67.984368212422694</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>67.775607506417956</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>67.554478694117421</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>67.320508075688778</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>67.073167707123233</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>66.811867501526677</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>66.535945694153696</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>66.244657241348278</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>65.93715958242106</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>65.612494995996002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>65.269568501507251</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64.907119849998594</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>64.52368754827782</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64.117561955081186</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>63.686723088047366</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>63.228756555322953</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>62.74073737618388</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>62.219065248845979</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>61.65922381636102</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>61.055415967851332</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>60.399986645290568</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>59.682458365518542</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>58.887803753208971</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>57.993052538854535</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>56.959705453537524</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>55.713045500334204</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54.061164310337062</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6948-4FF0-B49D-3C44EBC8E5BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ElipseTabla!$E$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YC2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$C$14:$C$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>101.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>103.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>106.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>107.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>108.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>111.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>112.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>113.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>116.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>117.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>118.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>121.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>122.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>123.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>127.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>128.75</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>131.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>132.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>133.75</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>136.25</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>137.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>138.75</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>141.25</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>142.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>143.75</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>146.25</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>147.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>148.75</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>151.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>152.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>153.75</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>156.25</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>157.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>158.75</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$E$14:$E$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.004340748830288</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.017368652863667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.039100721660859</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.069565428164339</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.10880289619999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.156865167015567</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.213816549027058</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.279734056334618</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30.354707943122861</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30.438842342824159</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.532256022960553</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.635083268962916</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.747474913086791</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30.869599527918339</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>31.001644808036673</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>31.143819168358732</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.296353593780466</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>31.459503782260839</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>31.633552632888183</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>31.818813142273811</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32.015631787577306</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32.224392493582044</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>32.445521305882579</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32.679491924311222</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>32.926832292876767</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>33.188132498473323</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>33.464054305846304</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>33.755342758651722</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>34.06284041757894</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>34.387505004003998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>34.730431498492749</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>35.092880150001406</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>35.47631245172218</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35.882438044918814</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36.313276911952634</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.771243444677047</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.25926262381612</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>37.780934751154021</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>38.34077618363898</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>38.944584032148668</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>39.600013354709432</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>40.317541634481458</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>41.112196246791029</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>42.006947461145465</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>43.040294546462476</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>44.286954499665796</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>45.938835689662938</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6948-4FF0-B49D-3C44EBC8E5BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ElipseTabla!$G$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YC3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$F$14:$F$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>97.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>91.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>88.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>87.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>86.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>83.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>81.25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>76.25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>73.75</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>71.25</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>68.75</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>66.25</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>63.75</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61.25</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>58.75</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>57.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>56.25</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>53.75</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>51.25</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>48.75</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>47.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46.25</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>43.75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>42.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>41.25</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$G$14:$G$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69.995659251169712</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69.982631347136333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.960899278339141</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69.930434571835661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.89119710380001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.843134832984433</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.786183450972942</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>69.720265943665382</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69.645292056877139</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.561157657175841</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>69.467743977039447</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>69.364916731037084</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>69.252525086913209</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>69.130400472081661</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>68.998355191963327</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>68.856180831641268</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>68.703646406219534</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>68.540496217739161</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>68.366447367111817</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>68.181186857726189</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>67.984368212422694</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>67.775607506417956</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>67.554478694117421</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>67.320508075688778</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>67.073167707123233</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>66.811867501526677</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>66.535945694153696</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>66.244657241348278</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>65.93715958242106</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>65.612494995996002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>65.269568501507251</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64.907119849998594</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>64.52368754827782</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>64.117561955081186</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>63.686723088047366</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>63.228756555322953</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>62.74073737618388</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>62.219065248845979</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>61.65922381636102</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>61.055415967851332</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>60.399986645290568</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>59.682458365518542</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>58.887803753208971</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>57.993052538854535</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>56.959705453537524</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>55.713045500334204</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54.061164310337062</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6948-4FF0-B49D-3C44EBC8E5BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ElipseTabla!$H$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YC4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$F$14:$F$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>97.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>91.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>88.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>87.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>86.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>83.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>81.25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>76.25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>73.75</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>72.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>71.25</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>68.75</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>66.25</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>63.75</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>62.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>61.25</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>58.75</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>57.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>56.25</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>53.75</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>51.25</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>48.75</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>47.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46.25</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>43.75</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>42.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>41.25</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ElipseTabla!$H$14:$H$113</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.004340748830288</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.017368652863667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.039100721660859</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.069565428164339</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.10880289619999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.156865167015567</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.213816549027058</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.279734056334618</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30.354707943122861</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30.438842342824159</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.532256022960553</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.635083268962916</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.747474913086791</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30.869599527918339</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>31.001644808036673</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>31.143819168358732</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31.296353593780466</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>31.459503782260839</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>31.633552632888183</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>31.818813142273811</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32.015631787577306</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32.224392493582044</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>32.445521305882579</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32.679491924311222</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>32.926832292876767</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>33.188132498473323</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>33.464054305846304</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>33.755342758651722</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>34.06284041757894</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>34.387505004003998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>34.730431498492749</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>35.092880150001406</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>35.47631245172218</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35.882438044918814</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36.313276911952634</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.771243444677047</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.25926262381612</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>37.780934751154021</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>38.34077618363898</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>38.944584032148668</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>39.600013354709432</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>40.317541634481458</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>41.112196246791029</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>42.006947461145465</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>43.040294546462476</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>44.286954499665796</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>45.938835689662938</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6948-4FF0-B49D-3C44EBC8E5BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="539537231"/>
+        <c:axId val="539541551"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="539537231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO"/>
+                  <a:t>X</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-CO"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="539541551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="539541551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO"/>
+                  <a:t>Y</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-CO"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="539537231"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3742,10 +6627,7 @@
           <a:pPr>
             <a:defRPr sz="2880" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
@@ -3763,10 +6645,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.3059331219961141E-2"/>
-          <c:y val="8.7593059927872294E-2"/>
-          <c:w val="0.92196437263523878"/>
-          <c:h val="0.75309356241974179"/>
+          <c:x val="0.10864535636116826"/>
+          <c:y val="0.11796346021983684"/>
+          <c:w val="0.86584268680914822"/>
+          <c:h val="0.63768610620127886"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -6464,10 +9346,7 @@
                 <a:pPr>
                   <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -6496,10 +9375,7 @@
               <a:pPr>
                 <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -6534,10 +9410,7 @@
             <a:pPr>
               <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -6580,10 +9453,7 @@
                 <a:pPr>
                   <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -6612,10 +9482,7 @@
               <a:pPr>
                 <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -6650,10 +9517,7 @@
             <a:pPr>
               <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -6692,10 +9556,7 @@
           <a:pPr>
             <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
@@ -6733,6 +9594,9 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="2400">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
           <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
           <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
         </a:defRPr>
@@ -6743,7 +9607,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8115,10 +10979,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -8147,10 +11008,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -8185,10 +11043,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -8231,10 +11086,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -8263,10 +11115,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -8301,10 +11150,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -8353,6 +11199,9 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
           <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
           <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
         </a:defRPr>
@@ -8368,7 +11217,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -21843,6 +24692,9 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1100" b="0">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
           <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
           <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
         </a:defRPr>
@@ -21939,6 +24791,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -23526,10 +26418,526 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{B19712F2-8C9D-4334-9A45-634DD1EA633A}">
   <sheetPr/>
-  <sheetProtection algorithmName="SHA-512" hashValue="80Wk8mIkGtvocOSfSoQ/cP6WwO6+zqqZx2/DsZ+g0w5r/AbOi+kMSBzuO6fGhNyL9GK2oH0vNCDIt7JZVKRlJw==" saltValue="0Op0hTNJPVPS6TQkKB/jLQ==" spinCount="100000" content="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Chqh4acawaG/Lgs8LTJpnvu7nTk7LgOZuUxNX8mBJliy058qeAx2hH0z0v7V5ph0auj1WPUHLwg5BQnTvEx84A==" saltValue="9yoiET+5tYRZNjpIDmYV0A==" spinCount="100000" content="1" objects="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -24166,6 +27574,44 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>265044</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>72886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>159025</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>78878</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A635523-4421-4B05-AAAA-B1F046B9FEB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -28104,7 +31550,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FfUeUT/ytSI+MP0sjPtaLuFKtOiNluSaipzQS+By5N7vQzRHzVZXfTyAvC+BiKbAzPvfscuoeNgL/bJckJFLDw==" saltValue="fit/PRh93aHZCHNKt7IEKw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tk34mCRw82YyHzTCz4JIpI/rMKCrvwpOamN7DoWfU5rLX3BgEIwDr0LkwuFwCJ8wVGE62ToSIHoLcachpirR8w==" saltValue="Qxhj5EAK2Nem6LTN9H6oSg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -34373,7 +37819,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OoGLRczN4UuGvLZGoWvabFOWuweDcvletkuf3BL6Yvvi6afJDXCwkgApaS01yrCDGEtibhZpsNDy1DuEnCOTTg==" saltValue="PWee5U2j1BKeaNHocsraow==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6O94+H+EckdzV6DxjfrLYpKzSl9HsFRsrLaZR0xUzH5lkGCrimQTVBr1EQI9T+anUIDPuumO5tVYMMF3RtGgOg==" saltValue="jywQsE6G35/BIwwUJDSZsA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -38382,7 +41828,7 @@
         <v>0.55850536063818546</v>
       </c>
       <c r="D50" s="29">
-        <f t="shared" ref="D50:D81" si="12">IF(SIN(C50)&gt;$I$3,$I$3,(IF(SIN(C50)&lt;-$I$3,-$I$3,SIN(C50))))</f>
+        <f t="shared" ref="D50:D67" si="12">IF(SIN(C50)&gt;$I$3,$I$3,(IF(SIN(C50)&lt;-$I$3,-$I$3,SIN(C50))))</f>
         <v>0.5299192642332049</v>
       </c>
       <c r="E50" s="29">
@@ -57127,7 +60573,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kr/Y0EUDcvNIdqOmWFgN9J5NolWbfvVscHyexcpTLJ6taeVIDIQOlZyzBG4xp9ExWK5B7XEQDRGWnXkSIEm3Ig==" saltValue="EJ3I9a8yj3jdLNjeRoCFdw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oo4b13a5obUtqd+F2iSN9xaCVKlbChiJNZtqA0vya+Mq1i/8yXIJyN+6Y5daoqXcg5c8wafeym0+musO11ihUA==" saltValue="LYp7+C1IOw2cvMiaaqY9qg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
